--- a/human_validation/judge/kor/judge_D017_S005_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S005_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,103 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요 — 오늘 와주셔서 감사합니다. 먼저 무엇 때문에 오시게 됐는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제 헤어라인이랑 레스토랑 조명 아래에서 제 얼굴이 어떻게 보이는지에 대한 생각을 멈출 수가 없어요. 늙고 이상해 보이는 느낌이 들어요, 동료들은 그게 안 보인다고 하는데도요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 동료분들이 헤어라인이나 얼굴에서 이상한 점을 못 느낀다고 말씀하실 때, 그분들이 맞을 수도 있다고 생각하는 부분이 있으신가요, 아니면 자신이 보는 게 정말로 거기 있다고 완전히 확신하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 그러니까, 다들 안 보인다고는 하는데, 저는 그 말을 정말 믿을 수가 없어요. 그 조명 아래에서는 제 헤어라인이랑 얼굴이 그냥 늙고 이상해 보여요. 계속 그 생각만 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 완전히 정상적으로 보이는, 다른 조명에서 찍힌 본인의 선명한 사진이나 영상을 보신다면, 그게 헤어라인이나 얼굴에 대한 생각을 바꿀 것 같으신가요, 아니면 여전히 뭔가 잘못됐다고 확신하실 것 같으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 아마 여전히 뭔가 잘못됐다고 느낄 것 같아요. 사진은 괜찮아 보일지 몰라도, 그 레스토랑 조명 아래에서는 그냥 제 헤어라인이랑 얼굴이 늙고 이상하게 보여요. 거기에 집중하는 걸 멈출 수가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 헤어라인이나 얼굴이 어떻게 보이는지 외에, 사람들이 자신을 지켜보거나, 얘기하거나, 음모를 꾸민다는 것처럼 다른 사람들은 눈치채지 못하거나 동의하지 않는 강한 믿음을 가지고 계신 게 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 아니요, 그런 건 못 느꼈어요. 정말 제 외모에 대해서만 꽂혀 있는 거예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신체이형장애 (D017) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>진단명: 신체이형장애 (D017)
 인구통계: 성별 남성 / 나이 54 / 직업상태 host or hostess restaurant lounge or coffee shop / 최종학력 대학 재학
@@ -575,152 +663,30 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S067
-배경 서술: 랠프 매튜스는 이혼 후 다시 연애를 시작하고 레스토랑에서 눈에 띄는 홀 담당 역할을 계속 맡게 되면서, 결혼 생활이 안정적이던 시절에는 겪지 않았던 방식으로 외모가 평가받고 있다는 느낌을 받게 되었다. 그는 손님과 동료들은 거의 눈치채지 못하는 헤어라인과 얼굴 외모의 결함이라고 느끼는 것에 점점 더 집착하게 되었고, 근무 전 준비 과정은 반복적인 거울 확인, 사진 재촬영, 몸단장, 그리고 레스토랑 조명 아래에서 자신이 어떻게 보이는지 머릿속으로 반복 점검하는 행동으로 확대되었다. 그가 지각하기 시작하고, 갤러리 행사와 등산을 거절하며, 직원 단체 사진을 피하고, 20년에 걸쳐 쌓아온 차분한 손님 응대 역할에 대한 자신감을 잃어가면서 이 걱정은 임상적으로 유의미해졌다. 결근과 업무 공백에 대한 심각한 경고를 받은 후, 그는 레스토랑의 직원 지원 의뢰를 이용했고 정신과 진료로 안내받았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요 — 오늘 와주셔서 감사합니다. 먼저 무엇 때문에 오시게 됐는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제 헤어라인이랑 레스토랑 조명 아래에서 제 얼굴이 어떻게 보이는지에 대한 생각을 멈출 수가 없어요. 늙고 이상해 보이는 느낌이 들어요, 동료들은 그게 안 보인다고 하는데도요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 동료분들이 헤어라인이나 얼굴에서 이상한 점을 못 느낀다고 말씀하실 때, 그분들이 맞을 수도 있다고 생각하는 부분이 있으신가요, 아니면 자신이 보는 게 정말로 거기 있다고 완전히 확신하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 그러니까, 다들 안 보인다고는 하는데, 저는 그 말을 정말 믿을 수가 없어요. 그 조명 아래에서는 제 헤어라인이랑 얼굴이 그냥 늙고 이상해 보여요. 계속 그 생각만 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 완전히 정상적으로 보이는, 다른 조명에서 찍힌 본인의 선명한 사진이나 영상을 보신다면, 그게 헤어라인이나 얼굴에 대한 생각을 바꿀 것 같으신가요, 아니면 여전히 뭔가 잘못됐다고 확신하실 것 같으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 아마 여전히 뭔가 잘못됐다고 느낄 것 같아요. 사진은 괜찮아 보일지 몰라도, 그 레스토랑 조명 아래에서는 그냥 제 헤어라인이랑 얼굴이 늙고 이상하게 보여요. 거기에 집중하는 걸 멈출 수가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 헤어라인이나 얼굴이 어떻게 보이는지 외에, 사람들이 자신을 지켜보거나, 얘기하거나, 음모를 꾸민다는 것처럼 다른 사람들은 눈치채지 못하거나 동의하지 않는 강한 믿음을 가지고 계신 게 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 아니요, 그런 건 못 느꼈어요. 정말 제 외모에 대해서만 꽂혀 있는 거예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
+배경 서술: 랠프 매튜스는 이혼 후 다시 연애를 시작하고 레스토랑에서 눈에 띄는 홀 담당 역할을 계속 맡게 되면서, 결혼 생활이 안정적이던 시절에는 겪지 않았던 방식으로 외모가 평가받고 있다는 느낌을 받게 되었다. 그는 손님과 동료들은 거의 눈치채지 못하는 헤어라인과 얼굴 외모의 결함이라고 느끼는 것에 점점 더 집착하게 되었고, 근무 전 준비 과정은 반복적인 거울 확인, 사진 재촬영, 몸단장, 그리고 레스토랑 조명 아래에서 자신이 어떻게 보이는지 머릿속으로 반복 점검하는 행동으로 확대되었다. 그가 지각하기 시작하고, 갤러리 행사와 등산을 거절하며, 직원 단체 사진을 피하고, 20년에 걸쳐 쌓아온 차분한 손님 응대 역할에 대한 자신감을 잃어가면서 이 걱정은 임상적으로 유의미해졌다. 결근과 업무 공백에 대한 심각한 경고를 받은 후, 그는 레스토랑의 직원 지원 의뢰를 이용했고 정신과 진료로 안내받았다.
+표집된 증상 목록:
+  - S067 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.
+  - S068 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.</t>
+        </is>
+      </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 신체이형장애 (D017) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신체이형장애 (D017, ICD: F45.22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: dysmorphic_symptoms (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
-  확인된 근거: 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.
-  누락: 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.</t>
+          <t>의사의 최종 진단: 신체이형장애 (D017, ICD: F45.22)
+지속 기간 요건: None
+기능적 손상 요건: 없음
+추가 요건: None
+체크리스트 그룹: dysmorphic_symptoms (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
+확인된 근거:
+  - 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D017_S005_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S005_P002__claude-sonnet-5_kor.xlsx
@@ -649,6 +649,11 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -682,11 +687,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D017_S005_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S005_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
